--- a/Stato avanzamento settori PCB .xlsx
+++ b/Stato avanzamento settori PCB .xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="95">
   <si>
     <t>Settore</t>
   </si>
@@ -165,9 +165,6 @@
     <t>Pin uscita (solo 5)</t>
   </si>
   <si>
-    <t>Valutare inserire nel PCB 2 o più impronte x TC2030 di programmazione</t>
-  </si>
-  <si>
     <t>Fotprint</t>
   </si>
   <si>
@@ -274,14 +271,6 @@
   </si>
   <si>
     <t>Netclass</t>
-  </si>
-  <si>
-    <t>Da ordinare:
-- 2 0 3 PCB Assemblati
-- connettori amp seal
-- MAP
-- Sensore pressione
-- IGBT</t>
   </si>
   <si>
     <t>?</t>
@@ -801,6 +790,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -827,28 +837,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1151,21 +1140,21 @@
       <c r="B3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="61"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="66" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="68"/>
       <c r="N3" s="16"/>
       <c r="O3" s="3"/>
     </row>
@@ -1181,16 +1170,16 @@
         <v>39</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -1225,10 +1214,10 @@
         <v>40</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="65" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>82</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>40</v>
@@ -1251,11 +1240,11 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="66"/>
+        <v>76</v>
+      </c>
+      <c r="G8" s="60"/>
       <c r="H8" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
@@ -1275,9 +1264,9 @@
         <v>40</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G9" s="61"/>
       <c r="H9" s="11" t="s">
         <v>40</v>
       </c>
@@ -1299,10 +1288,10 @@
         <v>40</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G10" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G10" s="59" t="s">
+        <v>82</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>40</v>
@@ -1325,9 +1314,9 @@
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G11" s="60"/>
       <c r="H11" s="12" t="s">
         <v>40</v>
       </c>
@@ -1349,9 +1338,9 @@
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G12" s="61"/>
       <c r="H12" s="12" t="s">
         <v>40</v>
       </c>
@@ -1373,10 +1362,10 @@
         <v>40</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="69" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>82</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>40</v>
@@ -1394,16 +1383,16 @@
         <v>19</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="66"/>
+        <v>76</v>
+      </c>
+      <c r="G14" s="60"/>
       <c r="H14" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
@@ -1423,9 +1412,9 @@
         <v>40</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G15" s="61"/>
       <c r="H15" s="13" t="s">
         <v>40</v>
       </c>
@@ -1447,10 +1436,10 @@
         <v>40</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G16" s="59" t="s">
+        <v>82</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>40</v>
@@ -1473,9 +1462,9 @@
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G17" s="61"/>
       <c r="H17" s="12" t="s">
         <v>40</v>
       </c>
@@ -1497,10 +1486,10 @@
         <v>40</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="65" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G18" s="72" t="s">
+        <v>82</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>40</v>
@@ -1523,9 +1512,9 @@
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G19" s="61"/>
       <c r="H19" s="11" t="s">
         <v>40</v>
       </c>
@@ -1539,7 +1528,7 @@
     </row>
     <row r="20" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -1550,7 +1539,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
@@ -1571,9 +1560,9 @@
         <v>40</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="62" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="13" t="s">
@@ -1597,9 +1586,9 @@
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G22" s="61"/>
       <c r="H22" s="13" t="s">
         <v>40</v>
       </c>
@@ -1621,10 +1610,10 @@
         <v>40</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G23" s="59" t="s">
+        <v>82</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>40</v>
@@ -1647,9 +1636,9 @@
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G24" s="61"/>
       <c r="H24" s="12" t="s">
         <v>40</v>
       </c>
@@ -1671,10 +1660,10 @@
         <v>40</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="69" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>82</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>40</v>
@@ -1697,9 +1686,9 @@
         <v>40</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G26" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G26" s="60"/>
       <c r="H26" s="13" t="s">
         <v>40</v>
       </c>
@@ -1721,9 +1710,9 @@
         <v>40</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G27" s="60"/>
       <c r="H27" s="13" t="s">
         <v>40</v>
       </c>
@@ -1745,9 +1734,9 @@
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G28" s="61"/>
       <c r="H28" s="13" t="s">
         <v>40</v>
       </c>
@@ -1769,10 +1758,10 @@
         <v>40</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G29" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G29" s="59" t="s">
+        <v>82</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>40</v>
@@ -1795,9 +1784,9 @@
         <v>40</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G30" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G30" s="60"/>
       <c r="H30" s="12" t="s">
         <v>40</v>
       </c>
@@ -1819,9 +1808,9 @@
         <v>40</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G31" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G31" s="60"/>
       <c r="H31" s="12" t="s">
         <v>40</v>
       </c>
@@ -1843,9 +1832,9 @@
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G32" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G32" s="61"/>
       <c r="H32" s="12" t="s">
         <v>40</v>
       </c>
@@ -1867,10 +1856,10 @@
         <v>40</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G33" s="69" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G33" s="62" t="s">
+        <v>82</v>
       </c>
       <c r="H33" s="13" t="s">
         <v>40</v>
@@ -1885,7 +1874,7 @@
     </row>
     <row r="34" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="13" t="s">
@@ -1893,9 +1882,9 @@
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G34" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G34" s="61"/>
       <c r="H34" s="13" t="s">
         <v>40</v>
       </c>
@@ -1917,10 +1906,10 @@
         <v>40</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G35" s="70" t="s">
-        <v>86</v>
+        <v>82</v>
+      </c>
+      <c r="G35" s="73" t="s">
+        <v>84</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>40</v>
@@ -1943,9 +1932,9 @@
         <v>40</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G36" s="71"/>
+        <v>82</v>
+      </c>
+      <c r="G36" s="57"/>
       <c r="H36" s="12" t="s">
         <v>40</v>
       </c>
@@ -1967,9 +1956,9 @@
       </c>
       <c r="E37" s="12"/>
       <c r="F37" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G37" s="72"/>
+        <v>82</v>
+      </c>
+      <c r="G37" s="58"/>
       <c r="H37" s="12" t="s">
         <v>40</v>
       </c>
@@ -1991,10 +1980,10 @@
         <v>40</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G38" s="73" t="s">
-        <v>86</v>
+        <v>82</v>
+      </c>
+      <c r="G38" s="56" t="s">
+        <v>84</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>40</v>
@@ -2017,9 +2006,9 @@
         <v>40</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G39" s="71"/>
+        <v>82</v>
+      </c>
+      <c r="G39" s="57"/>
       <c r="H39" s="13" t="s">
         <v>40</v>
       </c>
@@ -2041,9 +2030,9 @@
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G40" s="72"/>
+        <v>82</v>
+      </c>
+      <c r="G40" s="58"/>
       <c r="H40" s="13" t="s">
         <v>40</v>
       </c>
@@ -2065,10 +2054,10 @@
         <v>40</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G41" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G41" s="59" t="s">
+        <v>82</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>40</v>
@@ -2091,9 +2080,9 @@
         <v>40</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G42" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G42" s="60"/>
       <c r="H42" s="12" t="s">
         <v>40</v>
       </c>
@@ -2115,9 +2104,9 @@
       </c>
       <c r="E43" s="12"/>
       <c r="F43" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G43" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G43" s="61"/>
       <c r="H43" s="12" t="s">
         <v>40</v>
       </c>
@@ -2131,7 +2120,7 @@
     </row>
     <row r="44" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="47" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -2139,10 +2128,10 @@
         <v>40</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G44" s="69" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G44" s="62" t="s">
+        <v>82</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>40</v>
@@ -2157,7 +2146,7 @@
     </row>
     <row r="45" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
@@ -2165,9 +2154,9 @@
         <v>40</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G45" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G45" s="60"/>
       <c r="H45" s="13" t="s">
         <v>40</v>
       </c>
@@ -2181,7 +2170,7 @@
     </row>
     <row r="46" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -2189,9 +2178,9 @@
         <v>40</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G46" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G46" s="60"/>
       <c r="H46" s="13" t="s">
         <v>40</v>
       </c>
@@ -2205,7 +2194,7 @@
     </row>
     <row r="47" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -2213,9 +2202,9 @@
         <v>40</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G47" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G47" s="60"/>
       <c r="H47" s="13" t="s">
         <v>40</v>
       </c>
@@ -2237,9 +2226,9 @@
         <v>40</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G48" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G48" s="60"/>
       <c r="H48" s="13" t="s">
         <v>40</v>
       </c>
@@ -2253,7 +2242,7 @@
     </row>
     <row r="49" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="13" t="s">
@@ -2261,11 +2250,11 @@
       </c>
       <c r="E49" s="13"/>
       <c r="F49" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G49" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G49" s="60"/>
       <c r="H49" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
@@ -2277,7 +2266,7 @@
     </row>
     <row r="50" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="13" t="s">
@@ -2285,11 +2274,11 @@
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G50" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G50" s="60"/>
       <c r="H50" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
@@ -2301,7 +2290,7 @@
     </row>
     <row r="51" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C51" s="13"/>
       <c r="D51" s="13" t="s">
@@ -2309,11 +2298,11 @@
       </c>
       <c r="E51" s="13"/>
       <c r="F51" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G51" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G51" s="60"/>
       <c r="H51" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
@@ -2325,7 +2314,7 @@
     </row>
     <row r="52" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C52" s="13"/>
       <c r="D52" s="13" t="s">
@@ -2333,11 +2322,11 @@
       </c>
       <c r="E52" s="13"/>
       <c r="F52" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G52" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G52" s="60"/>
       <c r="H52" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
@@ -2349,7 +2338,7 @@
     </row>
     <row r="53" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53" s="13"/>
       <c r="D53" s="13" t="s">
@@ -2357,11 +2346,11 @@
       </c>
       <c r="E53" s="13"/>
       <c r="F53" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G53" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G53" s="60"/>
       <c r="H53" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -2373,7 +2362,7 @@
     </row>
     <row r="54" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C54" s="13"/>
       <c r="D54" s="13" t="s">
@@ -2381,11 +2370,11 @@
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G54" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G54" s="61"/>
       <c r="H54" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
@@ -2405,10 +2394,10 @@
         <v>40</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G55" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G55" s="59" t="s">
+        <v>82</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>40</v>
@@ -2431,9 +2420,9 @@
       </c>
       <c r="E56" s="12"/>
       <c r="F56" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G56" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G56" s="61"/>
       <c r="H56" s="12" t="s">
         <v>40</v>
       </c>
@@ -2455,10 +2444,10 @@
         <v>40</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G57" s="69" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G57" s="62" t="s">
+        <v>82</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>40</v>
@@ -2481,9 +2470,9 @@
         <v>40</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G58" s="66"/>
+        <v>82</v>
+      </c>
+      <c r="G58" s="60"/>
       <c r="H58" s="13" t="s">
         <v>40</v>
       </c>
@@ -2497,7 +2486,7 @@
     </row>
     <row r="59" spans="2:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
@@ -2505,9 +2494,9 @@
         <v>40</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G59" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G59" s="61"/>
       <c r="H59" s="13" t="s">
         <v>40</v>
       </c>
@@ -2529,10 +2518,10 @@
         <v>40</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G60" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H60" s="12" t="s">
         <v>40</v>
@@ -2555,10 +2544,10 @@
         <v>40</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G61" s="69" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="G61" s="62" t="s">
+        <v>82</v>
       </c>
       <c r="H61" s="13" t="s">
         <v>40</v>
@@ -2581,9 +2570,9 @@
         <v>40</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G62" s="67"/>
+        <v>82</v>
+      </c>
+      <c r="G62" s="61"/>
       <c r="H62" s="13" t="s">
         <v>40</v>
       </c>
@@ -2605,10 +2594,10 @@
         <v>40</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G63" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H63" s="12" t="s">
         <v>40</v>
@@ -2631,10 +2620,10 @@
         <v>40</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G64" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H64" s="13" t="s">
         <v>40</v>
@@ -2649,7 +2638,7 @@
     </row>
     <row r="65" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C65" s="12"/>
       <c r="D65" s="12" t="s">
@@ -2657,13 +2646,13 @@
       </c>
       <c r="E65" s="12"/>
       <c r="F65" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G65" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
@@ -2675,7 +2664,7 @@
     </row>
     <row r="66" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C66" s="12"/>
       <c r="D66" s="12" t="s">
@@ -2683,13 +2672,13 @@
       </c>
       <c r="E66" s="12"/>
       <c r="F66" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G66" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I66" s="12"/>
       <c r="J66" s="12"/>
@@ -2701,7 +2690,7 @@
     </row>
     <row r="67" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C67" s="12"/>
       <c r="D67" s="12" t="s">
@@ -2709,13 +2698,13 @@
       </c>
       <c r="E67" s="12"/>
       <c r="F67" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G67" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
@@ -2727,7 +2716,7 @@
     </row>
     <row r="68" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C68" s="12"/>
       <c r="D68" s="12" t="s">
@@ -2735,13 +2724,13 @@
       </c>
       <c r="E68" s="12"/>
       <c r="F68" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G68" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I68" s="12"/>
       <c r="J68" s="12"/>
@@ -2753,7 +2742,7 @@
     </row>
     <row r="69" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C69" s="12"/>
       <c r="D69" s="12" t="s">
@@ -2761,13 +2750,13 @@
       </c>
       <c r="E69" s="12"/>
       <c r="F69" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G69" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
@@ -2779,7 +2768,7 @@
     </row>
     <row r="70" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C70" s="12"/>
       <c r="D70" s="12" t="s">
@@ -2787,13 +2776,13 @@
       </c>
       <c r="E70" s="12"/>
       <c r="F70" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G70" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I70" s="12"/>
       <c r="J70" s="12"/>
@@ -2805,7 +2794,7 @@
     </row>
     <row r="71" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C71" s="12"/>
       <c r="D71" s="12" t="s">
@@ -2813,13 +2802,13 @@
       </c>
       <c r="E71" s="12"/>
       <c r="F71" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G71" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
@@ -2831,7 +2820,7 @@
     </row>
     <row r="72" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C72" s="12"/>
       <c r="D72" s="12" t="s">
@@ -2839,13 +2828,13 @@
       </c>
       <c r="E72" s="12"/>
       <c r="F72" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G72" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I72" s="12"/>
       <c r="J72" s="12"/>
@@ -2857,7 +2846,7 @@
     </row>
     <row r="73" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12" t="s">
@@ -2865,13 +2854,13 @@
       </c>
       <c r="E73" s="12"/>
       <c r="F73" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G73" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
@@ -2883,7 +2872,7 @@
     </row>
     <row r="74" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C74" s="12"/>
       <c r="D74" s="12" t="s">
@@ -2891,13 +2880,13 @@
       </c>
       <c r="E74" s="12"/>
       <c r="F74" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G74" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I74" s="12"/>
       <c r="J74" s="12"/>
@@ -2909,7 +2898,7 @@
     </row>
     <row r="75" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C75" s="12"/>
       <c r="D75" s="12" t="s">
@@ -2917,13 +2906,13 @@
       </c>
       <c r="E75" s="12"/>
       <c r="F75" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G75" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
@@ -2935,7 +2924,7 @@
     </row>
     <row r="76" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12" t="s">
@@ -2943,13 +2932,13 @@
       </c>
       <c r="E76" s="12"/>
       <c r="F76" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G76" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I76" s="12"/>
       <c r="J76" s="12"/>
@@ -2961,7 +2950,7 @@
     </row>
     <row r="77" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C77" s="12"/>
       <c r="D77" s="12" t="s">
@@ -2969,13 +2958,13 @@
       </c>
       <c r="E77" s="12"/>
       <c r="F77" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G77" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I77" s="12"/>
       <c r="J77" s="12"/>
@@ -2987,7 +2976,7 @@
     </row>
     <row r="78" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C78" s="12"/>
       <c r="D78" s="12" t="s">
@@ -2995,13 +2984,13 @@
       </c>
       <c r="E78" s="12"/>
       <c r="F78" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G78" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I78" s="12"/>
       <c r="J78" s="12"/>
@@ -3013,7 +3002,7 @@
     </row>
     <row r="79" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C79" s="12"/>
       <c r="D79" s="12" t="s">
@@ -3021,13 +3010,13 @@
       </c>
       <c r="E79" s="12"/>
       <c r="F79" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G79" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I79" s="12"/>
       <c r="J79" s="12"/>
@@ -3039,7 +3028,7 @@
     </row>
     <row r="80" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="12"/>
       <c r="D80" s="12" t="s">
@@ -3047,13 +3036,13 @@
       </c>
       <c r="E80" s="12"/>
       <c r="F80" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G80" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I80" s="12"/>
       <c r="J80" s="12"/>
@@ -3065,7 +3054,7 @@
     </row>
     <row r="81" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C81" s="12"/>
       <c r="D81" s="12" t="s">
@@ -3073,13 +3062,13 @@
       </c>
       <c r="E81" s="12"/>
       <c r="F81" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G81" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I81" s="12"/>
       <c r="J81" s="12"/>
@@ -3091,7 +3080,7 @@
     </row>
     <row r="82" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C82" s="12"/>
       <c r="D82" s="12" t="s">
@@ -3099,13 +3088,13 @@
       </c>
       <c r="E82" s="12"/>
       <c r="F82" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G82" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I82" s="12"/>
       <c r="J82" s="12"/>
@@ -3117,7 +3106,7 @@
     </row>
     <row r="83" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C83" s="12"/>
       <c r="D83" s="12" t="s">
@@ -3125,13 +3114,13 @@
       </c>
       <c r="E83" s="12"/>
       <c r="F83" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G83" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I83" s="12"/>
       <c r="J83" s="12"/>
@@ -3203,7 +3192,7 @@
     </row>
     <row r="87" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C87" s="35" t="s">
         <v>40</v>
@@ -3283,13 +3272,13 @@
         <v>40</v>
       </c>
       <c r="F91" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G91" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I91" s="12"/>
       <c r="J91" s="12"/>
@@ -3309,13 +3298,13 @@
         <v>40</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G92" s="32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I92" s="11"/>
       <c r="J92" s="11"/>
@@ -3349,7 +3338,7 @@
     <row r="94" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="22"/>
       <c r="B94" s="47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C94" s="13"/>
       <c r="D94" s="13"/>
@@ -3437,7 +3426,7 @@
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="10"/>
       <c r="B98" s="52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C98" s="53"/>
       <c r="D98" s="54"/>
@@ -3460,7 +3449,7 @@
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="10"/>
       <c r="B99" s="52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C99" s="53"/>
       <c r="D99" s="54"/>
@@ -3483,7 +3472,7 @@
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="10"/>
       <c r="B100" s="52" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C100" s="53"/>
       <c r="D100" s="54"/>
@@ -3506,7 +3495,7 @@
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="10"/>
       <c r="B101" s="52" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C101" s="53"/>
       <c r="D101" s="54"/>
@@ -3529,7 +3518,7 @@
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="10"/>
       <c r="B102" s="52" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C102" s="53"/>
       <c r="D102" s="54"/>
@@ -3572,9 +3561,7 @@
     </row>
     <row r="104" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
-      <c r="B104" s="49" t="s">
-        <v>48</v>
-      </c>
+      <c r="B104" s="49"/>
       <c r="C104" s="14"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -3721,9 +3708,7 @@
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="10"/>
-      <c r="B111" s="56" t="s">
-        <v>85</v>
-      </c>
+      <c r="B111" s="63"/>
       <c r="C111" s="14"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
@@ -3744,7 +3729,7 @@
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="8"/>
-      <c r="B112" s="57"/>
+      <c r="B112" s="64"/>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>
@@ -3765,7 +3750,7 @@
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="8"/>
-      <c r="B113" s="57"/>
+      <c r="B113" s="64"/>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
@@ -3786,7 +3771,7 @@
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="8"/>
-      <c r="B114" s="57"/>
+      <c r="B114" s="64"/>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
@@ -3807,7 +3792,7 @@
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="8"/>
-      <c r="B115" s="57"/>
+      <c r="B115" s="64"/>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
@@ -3828,7 +3813,7 @@
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="8"/>
-      <c r="B116" s="57"/>
+      <c r="B116" s="64"/>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -3849,7 +3834,7 @@
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="8"/>
-      <c r="B117" s="57"/>
+      <c r="B117" s="64"/>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -3870,7 +3855,7 @@
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="8"/>
-      <c r="B118" s="57"/>
+      <c r="B118" s="64"/>
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -3891,7 +3876,7 @@
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="8"/>
-      <c r="B119" s="57"/>
+      <c r="B119" s="64"/>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -3912,7 +3897,7 @@
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="8"/>
-      <c r="B120" s="57"/>
+      <c r="B120" s="64"/>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -3933,7 +3918,7 @@
     </row>
     <row r="121" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="8"/>
-      <c r="B121" s="58"/>
+      <c r="B121" s="65"/>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -4059,26 +4044,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="G61:G62"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G25:G28"/>
+    <mergeCell ref="H3:M3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G13:G15"/>
     <mergeCell ref="G38:G40"/>
     <mergeCell ref="G41:G43"/>
     <mergeCell ref="G44:G54"/>
     <mergeCell ref="G55:G56"/>
     <mergeCell ref="B111:B121"/>
-    <mergeCell ref="H3:M3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G25:G28"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="G61:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
